--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N14_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0002T0006Z000C1N14_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>66.14684854861285</v>
+        <v>10.74886288914959</v>
       </c>
       <c r="D2" t="n">
-        <v>64.90334466679255</v>
+        <v>10.54679350835379</v>
       </c>
       <c r="E2" t="n">
-        <v>20.24031774853603</v>
+        <v>3.289051634137104</v>
       </c>
       <c r="F2" t="n">
-        <v>20.45657111138855</v>
+        <v>3.324192805600639</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>45.75233963715267</v>
+        <v>7.43475519103731</v>
       </c>
       <c r="D3" t="n">
-        <v>44.34990310016387</v>
+        <v>7.20685925377663</v>
       </c>
       <c r="E3" t="n">
-        <v>20.24031774853603</v>
+        <v>3.289051634137104</v>
       </c>
       <c r="F3" t="n">
-        <v>20.45657111138855</v>
+        <v>3.324192805600639</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>55.38236133901653</v>
+        <v>8.999633717590187</v>
       </c>
       <c r="D4" t="n">
-        <v>54.67097746362552</v>
+        <v>8.884033837839148</v>
       </c>
       <c r="E4" t="n">
-        <v>20.24031774853603</v>
+        <v>3.289051634137104</v>
       </c>
       <c r="F4" t="n">
-        <v>20.45657111138855</v>
+        <v>3.324192805600639</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>58.41193893141455</v>
+        <v>9.491940076354863</v>
       </c>
       <c r="D5" t="n">
-        <v>57.91475172542193</v>
+        <v>9.411147155381064</v>
       </c>
       <c r="E5" t="n">
-        <v>20.24031774853603</v>
+        <v>3.289051634137104</v>
       </c>
       <c r="F5" t="n">
-        <v>20.45657111138855</v>
+        <v>3.324192805600639</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.56000729064758</v>
+        <v>5.616001184730231</v>
       </c>
       <c r="D6" t="n">
-        <v>33.33571894661547</v>
+        <v>5.417054328825015</v>
       </c>
       <c r="E6" t="n">
-        <v>20.24031774853603</v>
+        <v>3.289051634137104</v>
       </c>
       <c r="F6" t="n">
-        <v>20.45657111138855</v>
+        <v>3.324192805600639</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>68.35656545900859</v>
+        <v>11.1079418870889</v>
       </c>
       <c r="D7" t="n">
-        <v>68.14129105067823</v>
+        <v>11.07295979573521</v>
       </c>
       <c r="E7" t="n">
-        <v>20.24031774853603</v>
+        <v>3.289051634137104</v>
       </c>
       <c r="F7" t="n">
-        <v>20.45657111138855</v>
+        <v>3.324192805600639</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>68.10182282822035</v>
+        <v>11.06654620958581</v>
       </c>
       <c r="D8" t="n">
-        <v>67.28855171924108</v>
+        <v>10.93438965437668</v>
       </c>
       <c r="E8" t="n">
-        <v>20.24031774853603</v>
+        <v>3.289051634137104</v>
       </c>
       <c r="F8" t="n">
-        <v>20.45657111138855</v>
+        <v>3.324192805600639</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>31.09426479023126</v>
+        <v>5.052818028412581</v>
       </c>
       <c r="D9" t="n">
-        <v>30.5013680996641</v>
+        <v>4.956472316195417</v>
       </c>
       <c r="E9" t="n">
-        <v>20.24031774853603</v>
+        <v>3.289051634137104</v>
       </c>
       <c r="F9" t="n">
-        <v>20.45657111138855</v>
+        <v>3.324192805600639</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>77.67393986014658</v>
+        <v>12.62201522727382</v>
       </c>
       <c r="D10" t="n">
-        <v>77.66867736456497</v>
+        <v>12.62116007174181</v>
       </c>
       <c r="E10" t="n">
-        <v>20.24031774853603</v>
+        <v>3.289051634137104</v>
       </c>
       <c r="F10" t="n">
-        <v>20.45657111138855</v>
+        <v>3.324192805600639</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>70.3426388019457</v>
+        <v>11.43067880531618</v>
       </c>
       <c r="D11" t="n">
-        <v>70.57674038236982</v>
+        <v>11.4687203121351</v>
       </c>
       <c r="E11" t="n">
-        <v>20.24031774853603</v>
+        <v>3.289051634137104</v>
       </c>
       <c r="F11" t="n">
-        <v>20.45657111138855</v>
+        <v>3.324192805600639</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>24.02924644976511</v>
+        <v>3.90475254808683</v>
       </c>
       <c r="D12" t="n">
-        <v>23.59850747783575</v>
+        <v>3.83475746514831</v>
       </c>
       <c r="E12" t="n">
-        <v>20.24031774853603</v>
+        <v>3.289051634137104</v>
       </c>
       <c r="F12" t="n">
-        <v>20.45657111138855</v>
+        <v>3.324192805600639</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>32.07077909453654</v>
+        <v>5.211501602862188</v>
       </c>
       <c r="D13" t="n">
-        <v>32.43732434714082</v>
+        <v>5.271065206410384</v>
       </c>
       <c r="E13" t="n">
-        <v>20.24031774853603</v>
+        <v>3.289051634137104</v>
       </c>
       <c r="F13" t="n">
-        <v>20.45657111138855</v>
+        <v>3.324192805600639</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>64.24094974015365</v>
+        <v>10.43915433277497</v>
       </c>
       <c r="D14" t="n">
-        <v>64.05209267267746</v>
+        <v>10.40846505931009</v>
       </c>
       <c r="E14" t="n">
-        <v>20.24031774853603</v>
+        <v>3.289051634137104</v>
       </c>
       <c r="F14" t="n">
-        <v>20.45657111138855</v>
+        <v>3.324192805600639</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>51.87332683880182</v>
+        <v>8.429415611305297</v>
       </c>
       <c r="D15" t="n">
-        <v>52.62426892036098</v>
+        <v>8.551443699558659</v>
       </c>
       <c r="E15" t="n">
-        <v>20.24031774853603</v>
+        <v>3.289051634137104</v>
       </c>
       <c r="F15" t="n">
-        <v>20.45657111138855</v>
+        <v>3.324192805600639</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>15.8157351782051</v>
+        <v>2.570056966458329</v>
       </c>
       <c r="D16" t="n">
-        <v>17.22203464670439</v>
+        <v>2.798580630089464</v>
       </c>
       <c r="E16" t="n">
-        <v>20.24031774853603</v>
+        <v>3.289051634137104</v>
       </c>
       <c r="F16" t="n">
-        <v>20.45657111138855</v>
+        <v>3.324192805600639</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>38.81190687379944</v>
+        <v>6.306934866992409</v>
       </c>
       <c r="D17" t="n">
-        <v>39.85169851090987</v>
+        <v>6.475901008022854</v>
       </c>
       <c r="E17" t="n">
-        <v>20.24031774853603</v>
+        <v>3.289051634137104</v>
       </c>
       <c r="F17" t="n">
-        <v>20.45657111138855</v>
+        <v>3.324192805600639</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>58.91200578892472</v>
+        <v>9.573200940700268</v>
       </c>
       <c r="D18" t="n">
-        <v>59.72124624968346</v>
+        <v>9.704702515573562</v>
       </c>
       <c r="E18" t="n">
-        <v>20.24031774853603</v>
+        <v>3.289051634137104</v>
       </c>
       <c r="F18" t="n">
-        <v>20.45657111138855</v>
+        <v>3.324192805600639</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>63.66302266166532</v>
+        <v>10.34524118252061</v>
       </c>
       <c r="D19" t="n">
-        <v>64.37664760068174</v>
+        <v>10.46120523511078</v>
       </c>
       <c r="E19" t="n">
-        <v>20.24031774853603</v>
+        <v>3.289051634137104</v>
       </c>
       <c r="F19" t="n">
-        <v>20.45657111138855</v>
+        <v>3.324192805600639</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>57.9129018369133</v>
+        <v>9.410846548498412</v>
       </c>
       <c r="D20" t="n">
-        <v>58.90186303172685</v>
+        <v>9.571552742655612</v>
       </c>
       <c r="E20" t="n">
-        <v>20.24031774853603</v>
+        <v>3.289051634137104</v>
       </c>
       <c r="F20" t="n">
-        <v>20.45657111138855</v>
+        <v>3.324192805600639</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>49.79200943745743</v>
+        <v>8.091201533586833</v>
       </c>
       <c r="D21" t="n">
-        <v>51.05508218939278</v>
+        <v>8.296450855776328</v>
       </c>
       <c r="E21" t="n">
-        <v>20.24031774853603</v>
+        <v>3.289051634137104</v>
       </c>
       <c r="F21" t="n">
-        <v>20.45657111138855</v>
+        <v>3.324192805600639</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>84.32030008094635</v>
+        <v>13.70204876315378</v>
       </c>
       <c r="D22" t="n">
-        <v>85.07051986232226</v>
+        <v>13.82395947762737</v>
       </c>
       <c r="E22" t="n">
-        <v>20.24031774853603</v>
+        <v>3.289051634137104</v>
       </c>
       <c r="F22" t="n">
-        <v>20.45657111138855</v>
+        <v>3.324192805600639</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>66.75478483988053</v>
+        <v>10.84765253648059</v>
       </c>
       <c r="D23" t="n">
-        <v>68.01651352720418</v>
+        <v>11.05268344817068</v>
       </c>
       <c r="E23" t="n">
-        <v>20.24031774853603</v>
+        <v>3.289051634137104</v>
       </c>
       <c r="F23" t="n">
-        <v>20.45657111138855</v>
+        <v>3.324192805600639</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>76.24487606014935</v>
+        <v>12.38979235977427</v>
       </c>
       <c r="D24" t="n">
-        <v>77.29743488146391</v>
+        <v>12.56083316823789</v>
       </c>
       <c r="E24" t="n">
-        <v>20.24031774853603</v>
+        <v>3.289051634137104</v>
       </c>
       <c r="F24" t="n">
-        <v>20.45657111138855</v>
+        <v>3.324192805600639</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>72.96687107869575</v>
+        <v>11.85711655028806</v>
       </c>
       <c r="D25" t="n">
-        <v>74.14707759644865</v>
+        <v>12.04890010942291</v>
       </c>
       <c r="E25" t="n">
-        <v>20.24031774853603</v>
+        <v>3.289051634137104</v>
       </c>
       <c r="F25" t="n">
-        <v>20.45657111138855</v>
+        <v>3.324192805600639</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>96.66971887299714</v>
+        <v>15.70882931686203</v>
       </c>
       <c r="D26" t="n">
-        <v>97.41765052004496</v>
+        <v>15.83036820950731</v>
       </c>
       <c r="E26" t="n">
-        <v>20.24031774853603</v>
+        <v>3.289051634137104</v>
       </c>
       <c r="F26" t="n">
-        <v>20.45657111138855</v>
+        <v>3.324192805600639</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>79.90288528626175</v>
+        <v>12.98421885901753</v>
       </c>
       <c r="D27" t="n">
-        <v>81.06452060735147</v>
+        <v>13.17298459869461</v>
       </c>
       <c r="E27" t="n">
-        <v>20.24031774853603</v>
+        <v>3.289051634137104</v>
       </c>
       <c r="F27" t="n">
-        <v>20.45657111138855</v>
+        <v>3.324192805600639</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>95.69976912007152</v>
+        <v>15.55121248201162</v>
       </c>
       <c r="D28" t="n">
-        <v>96.69320053354713</v>
+        <v>15.71264508670141</v>
       </c>
       <c r="E28" t="n">
-        <v>20.24031774853603</v>
+        <v>3.289051634137104</v>
       </c>
       <c r="F28" t="n">
-        <v>20.45657111138855</v>
+        <v>3.324192805600639</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
